--- a/NiemYet/BangThongTin.xlsx
+++ b/NiemYet/BangThongTin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\thuctd.github.io\NiemYet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560EA28E-1332-49B9-82E0-A50BBE3744CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17EBE4D-6A09-4AEF-86C7-5B6CC43E65DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
   <si>
     <t>ID</t>
   </si>
@@ -315,9 +315,6 @@
     <t>CÔNG TY ĐIỆN LỰC ĐỒNG NAI</t>
   </si>
   <si>
-    <t>ĐỘI QUẢN LÝ ĐIỆN XUÂN LỘC</t>
-  </si>
-  <si>
     <t>Quý khách hàng vui lòng quét mã QR để xem nội dung.
 Trường hợp không thực hiện được vui lòng yêu cầu nhân viên hỗ trợ</t>
   </si>
@@ -413,6 +410,15 @@
   </si>
   <si>
     <t>Hướng dẫn đăng kí để tham gia cơ chế DPPA trên cổng thông tin dịch vụ trực tuyến NSMO</t>
+  </si>
+  <si>
+    <t>Quyết định bãi bỏ Quyết định số 1126/QĐ-UBND ngày 22 tháng 4 năm 2024 Quy trình một cửa liên thông giữa Cơ quan Nhà nước và Đơn vị điện lực trong giải quyết thủ tục cấp điện qua lưới điện trung áp trên địa bàn tỉnh Đồng Nai</t>
+  </si>
+  <si>
+    <t>https://thuctd.github.io\NiemYet\02-UBNDTinh\260325-QD bai bo QD 1126 ve quy trinh 1 cua lien thong.pdf</t>
+  </si>
+  <si>
+    <t>ĐIỆN LỰC XUÂN LỘC</t>
   </si>
 </sst>
 </file>
@@ -487,7 +493,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -602,9 +608,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -613,6 +616,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1073,7 +1079,7 @@
   <cols>
     <col min="1" max="3" width="7.3984375" customWidth="1"/>
     <col min="4" max="4" width="63.19921875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="64" style="21" customWidth="1"/>
+    <col min="5" max="5" width="64" style="20" customWidth="1"/>
     <col min="6" max="6" width="37.59765625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1132,7 +1138,7 @@
       <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -1153,7 +1159,7 @@
       <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -1174,7 +1180,7 @@
       <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="20" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -1216,7 +1222,7 @@
       <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="20" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -1237,7 +1243,7 @@
       <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -1258,7 +1264,7 @@
       <c r="D9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="20" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -1279,7 +1285,7 @@
       <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="20" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -1300,7 +1306,7 @@
       <c r="D11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -1321,7 +1327,7 @@
       <c r="D12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="20" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -1342,7 +1348,7 @@
       <c r="D13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="20" t="s">
         <v>40</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -1363,7 +1369,7 @@
       <c r="D14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="20" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="10" t="s">
@@ -1384,7 +1390,7 @@
       <c r="D15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="6" t="s">
@@ -1426,7 +1432,7 @@
       <c r="D17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="20" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -1447,7 +1453,7 @@
       <c r="D18" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="20" t="s">
         <v>55</v>
       </c>
       <c r="F18" s="6" t="s">
@@ -1468,7 +1474,7 @@
       <c r="D19" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="20" t="s">
         <v>58</v>
       </c>
       <c r="F19" s="6" t="s">
@@ -1489,7 +1495,7 @@
       <c r="D20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="20" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1507,7 +1513,7 @@
       <c r="D21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="20" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1525,7 +1531,7 @@
       <c r="D22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="20" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1543,7 +1549,7 @@
       <c r="D23" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="20" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1561,7 +1567,7 @@
       <c r="D24" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="20" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1579,7 +1585,7 @@
       <c r="D25" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="20" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1615,7 +1621,7 @@
       <c r="D27" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="20" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1631,10 +1637,10 @@
         <v>2025</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>91</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1649,10 +1655,10 @@
         <v>2025</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="21" t="s">
         <v>93</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1667,10 +1673,10 @@
         <v>2025</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="21" t="s">
         <v>95</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,13 +1691,13 @@
         <v>2025</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1706,10 +1712,10 @@
         <v>2025</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1724,10 +1730,10 @@
         <v>2025</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1742,10 +1748,10 @@
         <v>2026</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,16 +1766,28 @@
         <v>2026</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <f t="shared" si="1"/>
         <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>3</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2133,6 +2151,7 @@
     <hyperlink ref="E33" r:id="rId12" xr:uid="{10EBA9A8-AA5A-4AAF-AA0D-D73061618A1E}"/>
     <hyperlink ref="E34" r:id="rId13" xr:uid="{7A427726-3B26-4B9A-8E9D-1BA7A831E6A6}"/>
     <hyperlink ref="E35" r:id="rId14" xr:uid="{5EC76AC2-8CF2-40AA-BCD8-F4DD2CC4639C}"/>
+    <hyperlink ref="E36" r:id="rId15" xr:uid="{B50A1A95-F41B-4A5C-B8CE-37B2826447C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2161,29 +2180,29 @@
       </c>
       <c r="G1" t="str">
         <f>VLOOKUP(F2,QR!A:F,5,0)</f>
-        <v>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\260112-89- NSMO - Huong dan thao tac dang ki tham gia co che DPPA web DVTT.pdf</v>
+        <v>https://thuctd.github.io\NiemYet\02-UBNDTinh\260325-QD bai bo QD 1126 ve quy trinh 1 cua lien thong.pdf</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F2" s="22">
-        <v>34</v>
+      <c r="F2" s="21">
+        <v>35</v>
       </c>
       <c r="G2" s="11" t="str">
         <f>"https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data="&amp;G1</f>
-        <v>https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data=https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\260112-89- NSMO - Huong dan thao tac dang ki tham gia co che DPPA web DVTT.pdf</v>
+        <v>https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data=https://thuctd.github.io\NiemYet\02-UBNDTinh\260325-QD bai bo QD 1126 ve quy trinh 1 cua lien thong.pdf</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="22"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="2:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="22"/>
+        <v>109</v>
+      </c>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="2:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="16"/>
@@ -2194,9 +2213,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="20" t="str">
+      <c r="B7" s="23" t="str">
         <f>UPPER(VLOOKUP(F2,QR!A:D,4,0))</f>
-        <v>HƯỚNG DẪN ĐĂNG KÍ ĐỂ THAM GIA CƠ CHẾ DPPA TRÊN CỔNG THÔNG TIN DỊCH VỤ TRỰC TUYẾN NSMO</v>
+        <v>QUYẾT ĐỊNH BÃI BỎ QUYẾT ĐỊNH SỐ 1126/QĐ-UBND NGÀY 22 THÁNG 4 NĂM 2024 QUY TRÌNH MỘT CỬA LIÊN THÔNG GIỮA CƠ QUAN NHÀ NƯỚC VÀ ĐƠN VỊ ĐIỆN LỰC TRONG GIẢI QUYẾT THỦ TỤC CẤP ĐIỆN QUA LƯỚI ĐIỆN TRUNG ÁP TRÊN ĐỊA BÀN TỈNH ĐỒNG NAI</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="204" customHeight="1" x14ac:dyDescent="0.25">
@@ -2210,7 +2229,7 @@
     </row>
     <row r="9" spans="2:7" ht="76.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2237,33 +2256,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="2:7" s="3" customFormat="1" ht="46.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="157.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2276,22 +2295,22 @@
     </row>
     <row r="4" spans="2:7" s="3" customFormat="1" ht="47.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.25">

--- a/NiemYet/BangThongTin.xlsx
+++ b/NiemYet/BangThongTin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\thuctd.github.io\NiemYet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17EBE4D-6A09-4AEF-86C7-5B6CC43E65DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77E28C5-0D0D-4763-B78B-D36AA267D09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -419,6 +419,13 @@
   </si>
   <si>
     <t>ĐIỆN LỰC XUÂN LỘC</t>
+  </si>
+  <si>
+    <t>Yêu cầu kỹ thuật kết nối nguồn điện mặt trời mái nhà tự sản 
+xuất, tự tiêu thụ với Hệ thống thu thập, giám sát, điều khiển và Hệ thống dữ liệu đo đếm</t>
+  </si>
+  <si>
+    <t>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\4097_PCĐN-KD-YeuCauKyThuatTSTT.zip</t>
   </si>
 </sst>
 </file>
@@ -611,14 +618,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -771,6 +778,7 @@
 <webImagesSrd xmlns="http://schemas.microsoft.com/office/spreadsheetml/2020/richdatawebimage" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <webImageSrd>
     <address r:id="rId1"/>
+    <blip r:id="rId2"/>
   </webImageSrd>
 </webImagesSrd>
 </file>
@@ -782,7 +790,7 @@
     <v>5</v>
   </rv>
   <rv s="1">
-    <v>-1</v>
+    <v>0</v>
     <v>1</v>
     <v>0</v>
     <v>0</v>
@@ -1795,6 +1803,18 @@
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
+      <c r="B37" s="2">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
@@ -2152,6 +2172,7 @@
     <hyperlink ref="E34" r:id="rId13" xr:uid="{7A427726-3B26-4B9A-8E9D-1BA7A831E6A6}"/>
     <hyperlink ref="E35" r:id="rId14" xr:uid="{5EC76AC2-8CF2-40AA-BCD8-F4DD2CC4639C}"/>
     <hyperlink ref="E36" r:id="rId15" xr:uid="{B50A1A95-F41B-4A5C-B8CE-37B2826447C6}"/>
+    <hyperlink ref="E37" r:id="rId16" xr:uid="{7A10A3C0-8480-4C23-AFC6-5EB7D3818C09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2170,7 +2191,7 @@
     <col min="3" max="3" width="7.09765625" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
     <col min="5" max="5" width="20.19921875" customWidth="1"/>
-    <col min="6" max="6" width="27.19921875" customWidth="1"/>
+    <col min="6" max="6" width="20.59765625" customWidth="1"/>
     <col min="7" max="7" width="58.19921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2180,29 +2201,29 @@
       </c>
       <c r="G1" t="str">
         <f>VLOOKUP(F2,QR!A:F,5,0)</f>
-        <v>https://thuctd.github.io\NiemYet\02-UBNDTinh\260325-QD bai bo QD 1126 ve quy trinh 1 cua lien thong.pdf</v>
+        <v>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\4097_PCĐN-KD-YeuCauKyThuatTSTT.zip</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F2" s="21">
-        <v>35</v>
+      <c r="F2" s="22">
+        <v>36</v>
       </c>
       <c r="G2" s="11" t="str">
         <f>"https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data="&amp;G1</f>
-        <v>https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data=https://thuctd.github.io\NiemYet\02-UBNDTinh\260325-QD bai bo QD 1126 ve quy trinh 1 cua lien thong.pdf</v>
+        <v>https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data=https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\4097_PCĐN-KD-YeuCauKyThuatTSTT.zip</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="21"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="2:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="2:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="16"/>
@@ -2213,9 +2234,13 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="str">
+      <c r="B7" s="21" t="str">
         <f>UPPER(VLOOKUP(F2,QR!A:D,4,0))</f>
-        <v>QUYẾT ĐỊNH BÃI BỎ QUYẾT ĐỊNH SỐ 1126/QĐ-UBND NGÀY 22 THÁNG 4 NĂM 2024 QUY TRÌNH MỘT CỬA LIÊN THÔNG GIỮA CƠ QUAN NHÀ NƯỚC VÀ ĐƠN VỊ ĐIỆN LỰC TRONG GIẢI QUYẾT THỦ TỤC CẤP ĐIỆN QUA LƯỚI ĐIỆN TRUNG ÁP TRÊN ĐỊA BÀN TỈNH ĐỒNG NAI</v>
+        <v>YÊU CẦU KỸ THUẬT KẾT NỐI NGUỒN ĐIỆN MẶT TRỜI MÁI NHÀ TỰ SẢN 
+XUẤT, TỰ TIÊU THỤ VỚI HỆ THỐNG THU THẬP, GIÁM SÁT, ĐIỀU KHIỂN VÀ HỆ THỐNG DỮ LIỆU ĐO ĐẾM</v>
+      </c>
+      <c r="E7">
+        <v>300000</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="204" customHeight="1" x14ac:dyDescent="0.25">
@@ -2256,14 +2281,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="2:7" s="3" customFormat="1" ht="46.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">

--- a/NiemYet/BangThongTin.xlsx
+++ b/NiemYet/BangThongTin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\thuctd.github.io\NiemYet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77E28C5-0D0D-4763-B78B-D36AA267D09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7FB098-94BA-49DC-A055-3A8ED78776F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>ID</t>
   </si>
@@ -426,6 +426,12 @@
   </si>
   <si>
     <t>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\4097_PCĐN-KD-YeuCauKyThuatTSTT.zip</t>
+  </si>
+  <si>
+    <t>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\260422-BCT-963QD-KhungGio.pdf</t>
+  </si>
+  <si>
+    <t>Quyết định 963/QĐ-BCT ngày 22 tháng 04 năm 2026 của Bộ Công thương về khung giờ cao điểm, thấp điểm và giờ bình thường của hệ thống điện quốc gia</t>
   </si>
 </sst>
 </file>
@@ -1821,6 +1827,18 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
+      <c r="B38" s="2">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -2173,6 +2191,7 @@
     <hyperlink ref="E35" r:id="rId14" xr:uid="{5EC76AC2-8CF2-40AA-BCD8-F4DD2CC4639C}"/>
     <hyperlink ref="E36" r:id="rId15" xr:uid="{B50A1A95-F41B-4A5C-B8CE-37B2826447C6}"/>
     <hyperlink ref="E37" r:id="rId16" xr:uid="{7A10A3C0-8480-4C23-AFC6-5EB7D3818C09}"/>
+    <hyperlink ref="E38" r:id="rId17" xr:uid="{CE393344-E185-4165-B9D1-7268F700711A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2201,16 +2220,16 @@
       </c>
       <c r="G1" t="str">
         <f>VLOOKUP(F2,QR!A:F,5,0)</f>
-        <v>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\4097_PCĐN-KD-YeuCauKyThuatTSTT.zip</v>
+        <v>https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\260422-BCT-963QD-KhungGio.pdf</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F2" s="22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="11" t="str">
         <f>"https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data="&amp;G1</f>
-        <v>https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data=https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\4097_PCĐN-KD-YeuCauKyThuatTSTT.zip</v>
+        <v>https://api.qrserver.com/v1/create-qr-code/?size=500x500&amp;data=https://thuctd.github.io\NiemYet\01-Bo-Nganh-Luat\260422-BCT-963QD-KhungGio.pdf</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2236,8 +2255,7 @@
     <row r="7" spans="2:7" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="str">
         <f>UPPER(VLOOKUP(F2,QR!A:D,4,0))</f>
-        <v>YÊU CẦU KỸ THUẬT KẾT NỐI NGUỒN ĐIỆN MẶT TRỜI MÁI NHÀ TỰ SẢN 
-XUẤT, TỰ TIÊU THỤ VỚI HỆ THỐNG THU THẬP, GIÁM SÁT, ĐIỀU KHIỂN VÀ HỆ THỐNG DỮ LIỆU ĐO ĐẾM</v>
+        <v>QUYẾT ĐỊNH 963/QĐ-BCT NGÀY 22 THÁNG 04 NĂM 2026 CỦA BỘ CÔNG THƯƠNG VỀ KHUNG GIỜ CAO ĐIỂM, THẤP ĐIỂM VÀ GIỜ BÌNH THƯỜNG CỦA HỆ THỐNG ĐIỆN QUỐC GIA</v>
       </c>
       <c r="E7">
         <v>300000</v>
